--- a/backtest_runs/20260410_193731/filter/BWCL/BWCL.xlsx
+++ b/backtest_runs/20260410_193731/filter/BWCL/BWCL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-3700.699999999994</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101945.8</v>
@@ -679,7 +679,7 @@
         <v>-6191.600000000004</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95754.20000000001</v>
@@ -863,7 +863,7 @@
         <v>-457.7000000000021</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>99068.5</v>
@@ -909,7 +909,7 @@
         <v>-1844.599999999996</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>97223.89999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-253.0000000000052</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97902.39999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-1626.099999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100402.5</v>
@@ -1231,7 +1231,7 @@
         <v>-524.3999999999937</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>99878.10000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-7019.600000000009</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>92858.5</v>
@@ -1323,7 +1323,7 @@
         <v>-722.1999999999969</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>92136.3</v>
@@ -1415,7 +1415,7 @@
         <v>-892.399999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91243.89999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-165.5999999999932</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>91605</v>
@@ -1645,7 +1645,7 @@
         <v>-929.2000000000047</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>99694.10000000001</v>
